--- a/output/pdf_financials_xlsx/WGO.xlsx
+++ b/output/pdf_financials_xlsx/WGO.xlsx
@@ -1344,31 +1344,31 @@
         <v>-0.297788</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.229843</v>
+        <v>-1.229843</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5.558898</v>
+        <v>-5.558898</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.318562</v>
+        <v>-0.318562</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>6.611096</v>
+        <v>-6.611096</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.212704</v>
+        <v>-1.212704</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.10341</v>
+        <v>-1.10341</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>2.215792</v>
+        <v>-2.215792</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2.509619</v>
+        <v>-2.509619</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3.853902</v>
+        <v>-3.853902</v>
       </c>
     </row>
     <row r="17">
@@ -1660,31 +1660,31 @@
         <v>-0.297788</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.229843</v>
+        <v>-1.229843</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.558898</v>
+        <v>-5.558898</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.318562</v>
+        <v>-0.318562</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>6.611096</v>
+        <v>-6.611096</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.212704</v>
+        <v>-1.212704</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.10341</v>
+        <v>-1.10341</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>2.215792</v>
+        <v>-2.215792</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2.509619</v>
+        <v>-2.509619</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3.853902</v>
+        <v>-3.853902</v>
       </c>
     </row>
     <row r="21">
@@ -1843,31 +1843,31 @@
         <v>-0.297788</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.229843</v>
+        <v>-1.229843</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>5.558898</v>
+        <v>-5.558898</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.318562</v>
+        <v>-0.318562</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>6.611096</v>
+        <v>-6.611096</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.212704</v>
+        <v>-1.212704</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.10341</v>
+        <v>-1.10341</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2.215792</v>
+        <v>-2.215792</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.509619</v>
+        <v>-2.509619</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3.853902</v>
+        <v>-3.853902</v>
       </c>
     </row>
     <row r="24">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-61.49215</v>
+        <v>61.49215</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-92.64830000000001</v>
+        <v>92.64830000000001</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-132.22192</v>
+        <v>132.22192</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-192.6951</v>
+        <v>192.6951</v>
       </c>
     </row>
     <row r="27">
@@ -2109,31 +2109,31 @@
         <v>-0.297788</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.229843</v>
+        <v>-1.229843</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.558898</v>
+        <v>-5.558898</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.318562</v>
+        <v>-0.318562</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>6.611096</v>
+        <v>-6.611096</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.212704</v>
+        <v>-1.212704</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.10341</v>
+        <v>-1.10341</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>2.215792</v>
+        <v>-2.215792</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.509619</v>
+        <v>-2.509619</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>3.853902</v>
+        <v>-3.853902</v>
       </c>
     </row>
     <row r="28">
@@ -2231,31 +2231,31 @@
         <v>-0.315312</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.240833</v>
+        <v>-1.218853</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.57758</v>
+        <v>-5.540216</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.331639</v>
+        <v>-0.305485</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6.62025</v>
+        <v>-6.601942</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.219112</v>
+        <v>-1.206296</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.107895</v>
+        <v>-1.098925</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>2.218932</v>
+        <v>-2.212652</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.511817</v>
+        <v>-2.507421</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3.85544</v>
+        <v>-3.852364</v>
       </c>
     </row>
     <row r="30">
@@ -2389,31 +2389,31 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -34065,31 +34065,31 @@
         </is>
       </c>
       <c r="N249" s="5" t="n">
-        <v>1.229843</v>
+        <v>-1.229843</v>
       </c>
       <c r="O249" s="5" t="n">
-        <v>5.558898</v>
+        <v>-5.558898</v>
       </c>
       <c r="P249" s="5" t="n">
-        <v>0.318562</v>
+        <v>-0.318562</v>
       </c>
       <c r="Q249" s="5" t="n">
-        <v>6.611096</v>
+        <v>-6.611096</v>
       </c>
       <c r="R249" s="5" t="n">
-        <v>1.212704</v>
+        <v>-1.212704</v>
       </c>
       <c r="S249" s="5" t="n">
-        <v>1.10341</v>
+        <v>-1.10341</v>
       </c>
       <c r="T249" s="5" t="n">
-        <v>2.215792</v>
+        <v>-2.215792</v>
       </c>
       <c r="U249" s="5" t="n">
-        <v>2.509619</v>
+        <v>-2.509619</v>
       </c>
       <c r="V249" s="5" t="n">
-        <v>3.853902</v>
+        <v>-3.853902</v>
       </c>
     </row>
     <row r="250">

--- a/output/pdf_financials_xlsx/WGO.xlsx
+++ b/output/pdf_financials_xlsx/WGO.xlsx
@@ -1079,28 +1079,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003723</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000267</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000133</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000134</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000628</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006997</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.171487</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1118,13 +1118,13 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.150252</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.114823</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07915999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2088,28 +2088,28 @@
         <v>-1.456122</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.10833</v>
+        <v>-1.112053</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.258324</v>
+        <v>-1.258602</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.201327</v>
+        <v>-0.201594</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.102854</v>
+        <v>-0.102987</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.113595</v>
+        <v>-0.113729</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.1458</v>
+        <v>-0.146428</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.297788</v>
+        <v>-0.304785</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.229843</v>
+        <v>-1.40133</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-5.558898</v>
@@ -2127,13 +2127,13 @@
         <v>-1.10341</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.215792</v>
+        <v>-2.06554</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.509619</v>
+        <v>-2.394796</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-3.853902</v>
+        <v>-3.774742</v>
       </c>
     </row>
     <row r="28">
@@ -2210,28 +2210,28 @@
         <v>-1.456122</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.10833</v>
+        <v>-1.112053</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.258324</v>
+        <v>-1.258602</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.201327</v>
+        <v>-0.201594</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.102854</v>
+        <v>-0.102987</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.113595</v>
+        <v>-0.113729</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.1458</v>
+        <v>-0.146428</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.315312</v>
+        <v>-0.322309</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.218853</v>
+        <v>-1.39034</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-5.540216</v>
@@ -2249,13 +2249,13 @@
         <v>-1.098925</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.212652</v>
+        <v>-2.0624</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.507421</v>
+        <v>-2.392598</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-3.852364</v>
+        <v>-3.773204</v>
       </c>
     </row>
     <row r="30">
@@ -33814,7 +33814,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -54134,7 +54134,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">

--- a/output/pdf_financials_xlsx/WGO.xlsx
+++ b/output/pdf_financials_xlsx/WGO.xlsx
@@ -766,28 +766,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.029921</v>
+        <v>0.09952900000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.003967</v>
+        <v>0.06912500000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.020352</v>
+        <v>0.08149199999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.001875</v>
+        <v>0.043091</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.102678</v>
+        <v>0.118109</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.013177</v>
+        <v>0.028543</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.017856</v>
+        <v>0.029517</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.007712</v>
+        <v>0.011935</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.000156</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.165569</v>
+        <v>0.235177</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.095973</v>
+        <v>0.161131</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.117219</v>
+        <v>0.178359</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.502773</v>
@@ -967,10 +967,10 @@
         <v>0.102854</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.017856</v>
+        <v>0.029517</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.007712</v>
+        <v>0.011935</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.000156</v>
@@ -1030,10 +1030,10 @@
         <v>-0.102854</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.017856</v>
+        <v>-0.029517</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.007712</v>
+        <v>-0.011935</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.000156</v>
@@ -7208,31 +7208,31 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.112869</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.341913</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.997143</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>1.986634</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>-1.79771</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>-1.619029</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.133255</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.132147</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>2.059391</v>
       </c>
     </row>
     <row r="111">
@@ -20118,7 +20118,11 @@
           <t>Fair value adjustment and accretion expense</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21236,7 +21240,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -22426,7 +22434,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23102,7 +23114,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -23930,7 +23946,11 @@
           <t>Advance royalty accretion expense</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -24036,7 +24056,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -50278,7 +50302,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E405" s="5" t="n">
         <v>0.069608</v>
       </c>
